--- a/결과집계표.xlsx
+++ b/결과집계표.xlsx
@@ -30,9 +30,10 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="0037474F"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -42,65 +43,95 @@
     <fill>
       <gradientFill type="linear">
         <stop position="0">
-          <color rgb="00DCEFFB"/>
+          <color rgb="00F5F5F5"/>
         </stop>
         <stop position="1">
-          <color rgb="00E8DAEF"/>
+          <color rgb="00E8EAF6"/>
         </stop>
       </gradientFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00AED6F1"/>
-        <bgColor rgb="00AED6F1"/>
+        <fgColor rgb="00E3F2FD"/>
+        <bgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00A9DFBF"/>
-        <bgColor rgb="00A9DFBF"/>
+        <fgColor rgb="00BBDEFB"/>
+        <bgColor rgb="00BBDEFB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F9E79F"/>
-        <bgColor rgb="00F9E79F"/>
+        <fgColor rgb="00E8F5E8"/>
+        <bgColor rgb="00E8F5E8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5CBA7"/>
-        <bgColor rgb="00F5CBA7"/>
+        <fgColor rgb="00C8E6C9"/>
+        <bgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D2B4DE"/>
-        <bgColor rgb="00D2B4DE"/>
+        <fgColor rgb="00F3E5F5"/>
+        <bgColor rgb="00F3E5F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00A9CCE3"/>
-        <bgColor rgb="00A9CCE3"/>
+        <fgColor rgb="00E1BEE7"/>
+        <bgColor rgb="00E1BEE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FADBD8"/>
-        <bgColor rgb="00FADBD8"/>
+        <fgColor rgb="00FFF3E0"/>
+        <bgColor rgb="00FFF3E0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D7BDE2"/>
-        <bgColor rgb="00D7BDE2"/>
+        <fgColor rgb="00FFE0B2"/>
+        <bgColor rgb="00FFE0B2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E0F2F1"/>
+        <bgColor rgb="00E0F2F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B2DFDB"/>
+        <bgColor rgb="00B2DFDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8EAF6"/>
+        <bgColor rgb="00E8EAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C5CAE9"/>
+        <bgColor rgb="00C5CAE9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFDE7"/>
+        <bgColor rgb="00FFFDE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -113,16 +144,24 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00E0E0E0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -133,10 +172,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -158,6 +197,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -247,6 +301,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
   <chart>
     <title>
       <tx>
@@ -277,12 +332,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'학교통계'!$A$77:$A$87</f>
+              <f>'학교통계'!$A$91:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'학교통계'!$B$77:$B$87</f>
+              <f>'학교통계'!$B$91:$B$103</f>
             </numRef>
           </val>
         </ser>
@@ -299,6 +354,21 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>교과(군)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -311,6 +381,21 @@
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>평균 시수</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -324,7 +409,7 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="3"/>
+  <style val="8"/>
   <chart>
     <title>
       <tx>
@@ -354,20 +439,22 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'학교통계'!$A$89:$A$92</f>
+              <f>'학교통계'!$A$105:$A$109</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'학교통계'!$B$89:$B$92</f>
+              <f>'학교통계'!$B$105:$B$109</f>
             </numRef>
           </val>
         </ser>
         <dLbls>
+          <showVal val="0"/>
+          <showCatName val="1"/>
           <showPercent val="1"/>
         </dLbls>
         <firstSliceAng val="0"/>
-        <holeSize val="10"/>
+        <holeSize val="40"/>
       </doughnutChart>
     </plotArea>
     <legend>
@@ -388,7 +475,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4320000" cy="2880000"/>
+    <ext cx="5400000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -410,7 +497,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4320000" cy="2880000"/>
+    <ext cx="5400000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -717,12 +804,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -787,20 +874,20 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>강진주</t>
+          <t>강연우</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>영어 회화</t>
+          <t>통합사회1</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>사회</t>
         </is>
       </c>
     </row>
@@ -812,20 +899,20 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>김다은</t>
+          <t>강진주</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>통합과학1</t>
+          <t>영어 회화</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>과학</t>
+          <t>영어</t>
         </is>
       </c>
     </row>
@@ -837,20 +924,20 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>김다은</t>
+          <t>강진주</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>화학Ⅰ</t>
+          <t>실용 영어</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>과학</t>
+          <t>영어</t>
         </is>
       </c>
     </row>
@@ -867,11 +954,11 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>화학Ⅱ</t>
+          <t>통합과학1</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -887,20 +974,20 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>김미연</t>
+          <t>김다은</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>한국사1</t>
+          <t>화학Ⅰ</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>사회</t>
+          <t>과학</t>
         </is>
       </c>
     </row>
@@ -912,20 +999,20 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>김수옥</t>
+          <t>김다은</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>공통수학1</t>
+          <t>화학Ⅱ</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>수학</t>
+          <t>과학</t>
         </is>
       </c>
     </row>
@@ -937,16 +1024,16 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>김준수</t>
+          <t>김미연</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>세계사</t>
+          <t>한국사1</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -962,20 +1049,20 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>김진영</t>
+          <t>김소형</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>언어와 매체</t>
+          <t>* 원천징수</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>국어</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -987,20 +1074,20 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>김현아</t>
+          <t>김소형</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>사회·문화</t>
+          <t>기업 자원 통합 관리</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>사회</t>
+          <t>전문 교과</t>
         </is>
       </c>
     </row>
@@ -1012,20 +1099,20 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>김현아</t>
+          <t>김소형</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>정치와 법</t>
+          <t>세무 일반</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>사회</t>
+          <t>전문 교과</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1124,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>김희진</t>
+          <t>김수옥</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>공통영어1</t>
+          <t>공통수학1</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
@@ -1050,7 +1137,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>수학</t>
         </is>
       </c>
     </row>
@@ -1062,16 +1149,16 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>남궁연</t>
+          <t>김수옥</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>기하</t>
+          <t>기본수학1</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -1087,12 +1174,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>남궁연</t>
+          <t>김원홍</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>미적분</t>
+          <t>기업과 경영</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
@@ -1100,7 +1187,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>수학</t>
+          <t>전문 교과</t>
         </is>
       </c>
     </row>
@@ -1112,20 +1199,20 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>남궁연</t>
+          <t>김원홍</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>수학과제 탐구</t>
+          <t>유통 일반</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>수학</t>
+          <t>전문 교과</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1224,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>남궁연</t>
+          <t>김준수</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>확률과 통계</t>
+          <t>세계사</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
@@ -1150,7 +1237,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>수학</t>
+          <t>사회</t>
         </is>
       </c>
     </row>
@@ -1162,20 +1249,20 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>박선아</t>
+          <t>김준수</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>마케팅과 광고</t>
+          <t>한국사1</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>전문 교과</t>
+          <t>사회</t>
         </is>
       </c>
     </row>
@@ -1187,16 +1274,16 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>박찬들</t>
+          <t>김진영</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>문학</t>
+          <t>언어와 매체</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -1212,20 +1299,20 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>박현주</t>
+          <t>김진영</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>공통수학1</t>
+          <t>공통국어1</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>수학</t>
+          <t>국어</t>
         </is>
       </c>
     </row>
@@ -1237,20 +1324,20 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>박형빈</t>
+          <t>김현아</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>공통국어1</t>
+          <t>사회·문화</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>국어</t>
+          <t>사회</t>
         </is>
       </c>
     </row>
@@ -1262,20 +1349,20 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>박형빈</t>
+          <t>김현아</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>현대문학 감상</t>
+          <t>정치와 법</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>국어</t>
+          <t>사회</t>
         </is>
       </c>
     </row>
@@ -1287,20 +1374,20 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>반철진</t>
+          <t>김혜주</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>생활과 윤리</t>
+          <t>* 보고업무</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>사회</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -1312,20 +1399,20 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>성다나</t>
+          <t>김혜주</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>미술 감상과 비평</t>
+          <t>* 비품관리</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>예술</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -1337,20 +1424,20 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>성다나</t>
+          <t>김혜주</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>미술 창작</t>
+          <t>* 용역관리</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>예술</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1449,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>신민경</t>
+          <t>김혜주</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>여행지리</t>
+          <t>* 응대업무</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -1375,7 +1462,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>사회</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -1387,20 +1474,20 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>신민경</t>
+          <t>김혜주</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>한국지리</t>
+          <t>회계 정보 처리 시스템</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>사회</t>
+          <t>전문 교과</t>
         </is>
       </c>
     </row>
@@ -1412,16 +1499,16 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>신현선</t>
+          <t>김희진</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>영어 독해와 작문</t>
+          <t>공통영어1</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -1437,20 +1524,20 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>안경일</t>
+          <t>김희진</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>스포츠 생활</t>
+          <t>기본영어1</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>체육</t>
+          <t>영어</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1549,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>안경일</t>
+          <t>남궁연</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>체육 전공 실기 기초</t>
+          <t>기하</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -1475,7 +1562,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>체육</t>
+          <t>수학</t>
         </is>
       </c>
     </row>
@@ -1487,20 +1574,20 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>안경일</t>
+          <t>남궁연</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>체육1</t>
+          <t>미적분</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>체육</t>
+          <t>수학</t>
         </is>
       </c>
     </row>
@@ -1512,20 +1599,20 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>오영서</t>
+          <t>남궁연</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>지구과학Ⅰ</t>
+          <t>수학과제 탐구</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>과학</t>
+          <t>수학</t>
         </is>
       </c>
     </row>
@@ -1537,20 +1624,20 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>오영서</t>
+          <t>남궁연</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>지구과학Ⅱ</t>
+          <t>확률과 통계</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>과학</t>
+          <t>수학</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1649,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>윤아름</t>
+          <t>문기현</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>한문Ⅰ</t>
+          <t>* 자금관리</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -1575,7 +1662,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>한문</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -1587,20 +1674,20 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>윤인수</t>
+          <t>문기현</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>과학탐구실험1</t>
+          <t>* 전표관리</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>과학</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -1612,20 +1699,20 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>윤인수</t>
+          <t>문기현</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>물리학Ⅰ</t>
+          <t>상업 경제</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>과학</t>
+          <t>전문 교과</t>
         </is>
       </c>
     </row>
@@ -1637,20 +1724,20 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>윤인수</t>
+          <t>박선아</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>물리학Ⅱ</t>
+          <t>마케팅과 광고</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>과학</t>
+          <t>전문 교과</t>
         </is>
       </c>
     </row>
@@ -1662,20 +1749,20 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>윤인수</t>
+          <t>박선아</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>통합과학1</t>
+          <t>마케팅과 광고</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>과학</t>
+          <t>전문 교과</t>
         </is>
       </c>
     </row>
@@ -1687,20 +1774,20 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>이기홍</t>
+          <t>박선아</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>사회·문화</t>
+          <t>사무 관리</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>사회</t>
+          <t>전문 교과</t>
         </is>
       </c>
     </row>
@@ -1712,12 +1799,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>이기홍</t>
+          <t>박찬들</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>통합사회1</t>
+          <t>문학</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -1725,7 +1812,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>사회</t>
+          <t>국어</t>
         </is>
       </c>
     </row>
@@ -1737,20 +1824,20 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>이미경</t>
+          <t>박찬들</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>공통영어1</t>
+          <t>공통국어1</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>국어</t>
         </is>
       </c>
     </row>
@@ -1762,20 +1849,20 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>이선주</t>
+          <t>박찬들</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>영어Ⅰ</t>
+          <t>실용 국어</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>국어</t>
         </is>
       </c>
     </row>
@@ -1787,12 +1874,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>이수종</t>
+          <t>박현주</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>화법과 작문</t>
+          <t>공통수학1</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -1800,7 +1887,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>국어</t>
+          <t>수학</t>
         </is>
       </c>
     </row>
@@ -1812,20 +1899,20 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>이애림</t>
+          <t>박현주</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>심리학</t>
+          <t>기본수학1</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>교양</t>
+          <t>수학</t>
         </is>
       </c>
     </row>
@@ -1837,20 +1924,20 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>이애림</t>
+          <t>박형빈</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>확률과 통계</t>
+          <t>공통국어1</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>수학</t>
+          <t>국어</t>
         </is>
       </c>
     </row>
@@ -1862,16 +1949,16 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>이은영</t>
+          <t>박형빈</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>문학</t>
+          <t>현대문학 감상</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -1887,16 +1974,16 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>이현솔</t>
+          <t>반철진</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>세계지리</t>
+          <t>생활과 윤리</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -1912,7 +1999,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>이현솔</t>
+          <t>반철진</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1921,7 +2008,7 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -1937,20 +2024,20 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>이현정</t>
+          <t>배서연</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>수학Ⅰ</t>
+          <t>* 문서관리</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>수학</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -1962,20 +2049,20 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>임건</t>
+          <t>배서연</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>미디어 콘텐츠 일반</t>
+          <t>* 문서작성</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>전문 교과</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -1987,20 +2074,20 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>임영수</t>
+          <t>배서연</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>교육학</t>
+          <t>기업과 경영</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>교양</t>
+          <t>전문 교과</t>
         </is>
       </c>
     </row>
@@ -2012,20 +2099,20 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>임영수</t>
+          <t>성다나</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>스포츠 생활</t>
+          <t>미술 감상과 비평</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>체육</t>
+          <t>예술</t>
         </is>
       </c>
     </row>
@@ -2037,20 +2124,20 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>임영수</t>
+          <t>성다나</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>운동과 건강</t>
+          <t>미술 창작</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>체육</t>
+          <t>예술</t>
         </is>
       </c>
     </row>
@@ -2062,20 +2149,20 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>임영수</t>
+          <t>성다나</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>체육1</t>
+          <t>미술 창작</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>체육</t>
+          <t>예술</t>
         </is>
       </c>
     </row>
@@ -2087,20 +2174,20 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>장유진</t>
+          <t>신민경</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>공통국어1</t>
+          <t>여행지리</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>국어</t>
+          <t>사회</t>
         </is>
       </c>
     </row>
@@ -2112,20 +2199,20 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>전형구</t>
+          <t>신민경</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>생명과학Ⅱ</t>
+          <t>한국지리</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>과학</t>
+          <t>사회</t>
         </is>
       </c>
     </row>
@@ -2137,20 +2224,20 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>전형구</t>
+          <t>신민경</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>생활과 과학</t>
+          <t>통합사회1</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>과학</t>
+          <t>사회</t>
         </is>
       </c>
     </row>
@@ -2162,20 +2249,20 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>전형구</t>
+          <t>신현선</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>영어 독해와 작문</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>교양</t>
+          <t>영어</t>
         </is>
       </c>
     </row>
@@ -2187,20 +2274,20 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>정다혜</t>
+          <t>신현선</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>수학Ⅰ</t>
+          <t>실용 영어</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>수학</t>
+          <t>영어</t>
         </is>
       </c>
     </row>
@@ -2212,20 +2299,20 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>정다혜</t>
+          <t>안경일</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>실용 경제</t>
+          <t>스포츠 생활</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>교양</t>
+          <t>체육</t>
         </is>
       </c>
     </row>
@@ -2237,16 +2324,16 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>정대교</t>
+          <t>안경일</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>스포츠 생활</t>
+          <t>체육 전공 실기 기초</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -2262,12 +2349,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>정대교</t>
+          <t>안경일</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>운동과 건강</t>
+          <t>체육1</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
@@ -2287,16 +2374,16 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>정대교</t>
+          <t>안경일</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>체육1</t>
+          <t>운동과 건강</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -2312,20 +2399,20 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>정래호</t>
+          <t>안경일</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>영어Ⅰ</t>
+          <t>체육1</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>체육</t>
         </is>
       </c>
     </row>
@@ -2337,20 +2424,20 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>정래호</t>
+          <t>엄미희</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>영어권 문화</t>
+          <t>* 캐릭터 그래픽 요소 제작</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -2362,12 +2449,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>정빛나</t>
+          <t>엄미희</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>과학탐구실험1</t>
+          <t>* 캐릭터 콘셉트 설정</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
@@ -2375,7 +2462,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>과학</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -2387,20 +2474,20 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>정빛나</t>
+          <t>엄미희</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>생명과학Ⅰ</t>
+          <t>미디어 콘텐츠 일반</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>과학</t>
+          <t>전문 교과</t>
         </is>
       </c>
     </row>
@@ -2412,16 +2499,16 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>정빛나</t>
+          <t>오영서</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>통합과학1</t>
+          <t>지구과학Ⅰ</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -2437,20 +2524,20 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>천원영</t>
+          <t>오영서</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>동아시아사</t>
+          <t>지구과학Ⅱ</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>사회</t>
+          <t>과학</t>
         </is>
       </c>
     </row>
@@ -2462,20 +2549,20 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>최효진</t>
+          <t>윤아름</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>일본어Ⅰ</t>
+          <t>한문Ⅰ</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>제2외국어</t>
+          <t>한문</t>
         </is>
       </c>
     </row>
@@ -2487,20 +2574,20 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>허원아</t>
+          <t>윤인수</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>음악</t>
+          <t>과학탐구실험1</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>예술</t>
+          <t>과학</t>
         </is>
       </c>
     </row>
@@ -2512,20 +2599,20 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>허원아</t>
+          <t>윤인수</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>음악 감상과 비평</t>
+          <t>물리학Ⅰ</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>예술</t>
+          <t>과학</t>
         </is>
       </c>
     </row>
@@ -2537,18 +2624,1568 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
+          <t>윤인수</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>물리학Ⅱ</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>윤인수</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>통합과학1</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>이기홍</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>사회·문화</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>이기홍</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>통합사회1</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>이미경</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>공통영어1</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>영어</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>이미경</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>기본영어1</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>영어</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>이선주</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>영어Ⅰ</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>영어</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>이선주</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>실용 영어</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>영어</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>이수종</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>화법과 작문</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>국어</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>이수종</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>실용 국어</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>국어</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>이애림</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>심리학</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>교양</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>이애림</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>확률과 통계</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>수학</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>이애림</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>실용 수학</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>수학</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>이은영</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>문학</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>국어</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>이은영</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>실용 국어</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>국어</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>이현솔</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>세계지리</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>이현솔</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>통합사회1</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>이현정</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>수학Ⅰ</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>수학</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>이현정</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>실용 수학</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>수학</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>인창열</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>* 게임 웹 프로그래밍</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>인창열</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>* 게임 플랫폼 응용 프로그래밍</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>인창열</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>정보 처리와 관리</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>전문 교과</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>인창열</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>컴퓨터 시스템 일반</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>임건</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>미디어 콘텐츠 일반</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>전문 교과</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>임건</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>* 게임엔진 응용 프로그래밍</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>임건</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>디자인 일반</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>전문 교과</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>임건</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>정보 처리와 관리</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>전문 교과</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>임영수</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>교육학</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>교양</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>임영수</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>스포츠 생활</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>체육</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>임영수</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>운동과 건강</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>체육</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>임영수</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>체육1</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>체육</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>임영수</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>운동과 건강</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>체육</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>장유진</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>공통국어1</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>국어</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>장유진</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>공통국어1</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>국어</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>전정화</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>* 사업기획</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>전정화</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>* 사이트 기획</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>전정화</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>정보 처리와 관리</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>전문 교과</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>전정화</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>컴퓨터 그래픽</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>전문 교과</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>전형구</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>생명과학Ⅱ</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>전형구</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>생활과 과학</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>전형구</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>환경</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>교양</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>정다혜</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>수학Ⅰ</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>수학</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>정다혜</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>실용 경제</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>교양</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>정대교</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>스포츠 생활</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>체육</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>정대교</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>운동과 건강</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>체육</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>정대교</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>체육1</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>체육</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>정대교</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>운동과 건강</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>체육</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>정대교</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>체육1</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>체육</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>정래호</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>영어Ⅰ</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>영어</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>정래호</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>영어권 문화</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>영어</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>정빛나</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>과학탐구실험1</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>정빛나</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>생명과학Ⅰ</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>정빛나</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>통합과학1</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>정영신</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>* 고객 필요정보 제공</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>정영신</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>* 고객관리 계획수립</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>정영신</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>* 사무자동화 프로그램 활용</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>정영신</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>상업 경제</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>전문 교과</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>천원영</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>동아시아사</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>최효진</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>일본어Ⅰ</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>제2외국어</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>최효진</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>일본어Ⅰ</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>제2외국어</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>허원아</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>음악</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>예술</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>허원아</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>음악 감상과 비평</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>예술</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>황주현</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
         <is>
           <t>보건</t>
         </is>
       </c>
-      <c r="D73" s="2" t="n">
+      <c r="D135" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>교양</t>
         </is>
@@ -2565,7 +4202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2573,8 +4210,8 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2631,14 +4268,14 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>윤리와 사상</t>
+          <t>윤리와 사상, 통합사회1</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -2660,14 +4297,14 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>영어 회화</t>
+          <t>실용 영어, 영어 회화</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -2738,26 +4375,30 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>김수옥</t>
+          <t>김소형</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>수학</t>
+          <t>전문 교과</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>공통수학1</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
+          <t>* 원천징수, 기업 자원 통합 관리, 세무 일반</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>기타 + 전문 교과</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2767,23 +4408,23 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>김준수</t>
+          <t>김수옥</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>사회</t>
+          <t>수학</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>세계사</t>
+          <t>공통수학1, 기본수학1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -2796,23 +4437,23 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>김진영</t>
+          <t>김원홍</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>국어</t>
+          <t>전문 교과</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>언어와 매체</t>
+          <t>기업과 경영, 유통 일반</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -2825,7 +4466,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>김현아</t>
+          <t>김준수</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -2834,14 +4475,14 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>사회·문화, 정치와 법</t>
+          <t>세계사, 한국사1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -2854,23 +4495,23 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>김희진</t>
+          <t>김진영</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>국어</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>공통영어1</t>
+          <t>공통국어1, 언어와 매체</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -2883,23 +4524,23 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>남궁연</t>
+          <t>김현아</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>수학</t>
+          <t>사회</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>기하, 미적분, 수학과제 탐구, 확률과 통계</t>
+          <t>사회·문화, 정치와 법</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -2912,7 +4553,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>박선아</t>
+          <t>김혜주</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2921,17 +4562,21 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>마케팅과 광고</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
+          <t>* 보고업무, * 비품관리, * 용역관리, * 응대업무, 회계 정보 처리 시스템</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>기타 + 전문 교과</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2941,23 +4586,23 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>박찬들</t>
+          <t>김희진</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>국어</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>문학</t>
+          <t>공통영어1, 기본영어1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -2970,7 +4615,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>박현주</t>
+          <t>남궁연</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2979,14 +4624,14 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>공통수학1</t>
+          <t>기하, 미적분, 수학과제 탐구, 확률과 통계</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -2999,26 +4644,30 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>박형빈</t>
+          <t>문기현</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>국어</t>
+          <t>전문 교과</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>공통국어1, 현대문학 감상</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
+          <t>* 자금관리, * 전표관리, 상업 경제</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>기타 + 전문 교과</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3028,23 +4677,23 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>반철진</t>
+          <t>박선아</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>사회</t>
+          <t>전문 교과</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>생활과 윤리</t>
+          <t>마케팅과 광고, 사무 관리</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -3057,23 +4706,23 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>성다나</t>
+          <t>박찬들</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>예술</t>
+          <t>국어</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>미술 감상과 비평, 미술 창작</t>
+          <t>공통국어1, 문학, 실용 국어</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -3086,23 +4735,23 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>신민경</t>
+          <t>박현주</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>사회</t>
+          <t>수학</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>여행지리, 한국지리</t>
+          <t>공통수학1, 기본수학1</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -3115,23 +4764,23 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>신현선</t>
+          <t>박형빈</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>국어</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>영어 독해와 작문</t>
+          <t>공통국어1, 현대문학 감상</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -3144,23 +4793,23 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>안경일</t>
+          <t>반철진</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>체육</t>
+          <t>사회</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>스포츠 생활, 체육 전공 실기 기초, 체육1</t>
+          <t>생활과 윤리, 통합사회1</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -3173,26 +4822,30 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>오영서</t>
+          <t>배서연</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>과학</t>
+          <t>전문 교과</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>지구과학Ⅰ, 지구과학Ⅱ</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
+          <t>* 문서관리, * 문서작성, 기업과 경영</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>기타 + 전문 교과</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -3202,23 +4855,23 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>윤아름</t>
+          <t>성다나</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>한문</t>
+          <t>예술</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E22" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>한문Ⅰ</t>
+          <t>미술 감상과 비평, 미술 창작</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -3231,23 +4884,23 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>윤인수</t>
+          <t>신민경</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>과학</t>
+          <t>사회</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>과학탐구실험1, 물리학Ⅰ, 물리학Ⅱ, 통합과학1</t>
+          <t>여행지리, 통합사회1, 한국지리</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -3260,23 +4913,23 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>이기홍</t>
+          <t>신현선</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>사회</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>사회·문화, 통합사회1</t>
+          <t>실용 영어, 영어 독해와 작문</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -3289,23 +4942,23 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>이미경</t>
+          <t>안경일</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>체육</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
         <v>12</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>공통영어1</t>
+          <t>스포츠 생활, 운동과 건강, 체육 전공 실기 기초, 체육1</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -3318,26 +4971,30 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>이선주</t>
+          <t>엄미희</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>전문 교과</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>영어Ⅰ</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
+          <t>* 캐릭터 그래픽 요소 제작, * 캐릭터 콘셉트 설정, 미디어 콘텐츠 일반</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>기타 + 전문 교과</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -3347,23 +5004,23 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>이수종</t>
+          <t>오영서</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>국어</t>
+          <t>과학</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>화법과 작문</t>
+          <t>지구과학Ⅰ, 지구과학Ⅱ</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -3376,30 +5033,26 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>이애림</t>
+          <t>윤아름</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>수학</t>
+          <t>한문</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>심리학, 확률과 통계</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>교양 + 수학</t>
-        </is>
-      </c>
+          <t>한문Ⅰ</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3409,23 +5062,23 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>이은영</t>
+          <t>윤인수</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>국어</t>
+          <t>과학</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>문학</t>
+          <t>과학탐구실험1, 물리학Ⅰ, 물리학Ⅱ, 통합과학1</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -3438,7 +5091,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>이현솔</t>
+          <t>이기홍</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3447,14 +5100,14 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>세계지리, 통합사회1</t>
+          <t>사회·문화, 통합사회1</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -3467,23 +5120,23 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>이현정</t>
+          <t>이미경</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>수학</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>수학Ⅰ</t>
+          <t>공통영어1, 기본영어1</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -3496,23 +5149,23 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>임건</t>
+          <t>이선주</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>전문 교과</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>미디어 콘텐츠 일반</t>
+          <t>실용 영어, 영어Ⅰ</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -3525,30 +5178,26 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>임영수</t>
+          <t>이수종</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>체육</t>
+          <t>국어</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>교육학, 스포츠 생활, 운동과 건강, 체육1</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>교양 + 체육</t>
-        </is>
-      </c>
+          <t>실용 국어, 화법과 작문</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3558,26 +5207,30 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>장유진</t>
+          <t>이애림</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>국어</t>
+          <t>수학</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>공통국어1</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
+          <t>실용 수학, 심리학, 확률과 통계</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>교양 + 수학</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3587,30 +5240,26 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>전형구</t>
+          <t>이은영</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>과학</t>
+          <t>국어</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>생명과학Ⅱ, 생활과 과학, 환경</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>과학 + 교양</t>
-        </is>
-      </c>
+          <t>문학, 실용 국어</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3620,30 +5269,26 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>정다혜</t>
+          <t>이현솔</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>수학</t>
+          <t>사회</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>수학Ⅰ, 실용 경제</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>교양 + 수학</t>
-        </is>
-      </c>
+          <t>세계지리, 통합사회1</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3653,23 +5298,23 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>정대교</t>
+          <t>이현정</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>체육</t>
+          <t>수학</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>스포츠 생활, 운동과 건강, 체육1</t>
+          <t>수학Ⅰ, 실용 수학</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -3682,26 +5327,30 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>정래호</t>
+          <t>인창열</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>정보</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>영어Ⅰ, 영어권 문화</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
+          <t>* 게임 웹 프로그래밍, * 게임 플랫폼 응용 프로그래밍, 정보 처리와 관리, 컴퓨터 시스템 일반</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>전문 교과 + 정보</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3711,26 +5360,30 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>정빛나</t>
+          <t>임건</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>과학</t>
+          <t>정보</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>과학탐구실험1, 생명과학Ⅰ, 통합과학1</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
+          <t>* 게임엔진 응용 프로그래밍, 디자인 일반, 미디어 콘텐츠 일반, 정보 처리와 관리</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>전문 교과 + 정보</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3740,26 +5393,30 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>천원영</t>
+          <t>임영수</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>사회</t>
+          <t>체육</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>동아시아사</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
+          <t>교육학, 스포츠 생활, 운동과 건강, 체육1</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>교양 + 체육</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3769,23 +5426,23 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>최효진</t>
+          <t>장유진</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>제2외국어</t>
+          <t>국어</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>일본어Ⅰ</t>
+          <t>공통국어1</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -3798,26 +5455,30 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>허원아</t>
+          <t>전정화</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>예술</t>
+          <t>전문 교과</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>음악, 음악 감상과 비평</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
+          <t>* 사업기획, * 사이트 기획, 정보 처리와 관리, 컴퓨터 그래픽</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>기타 + 전문 교과</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3827,56 +5488,329 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
+          <t>전형구</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>생명과학Ⅱ, 생활과 과학, 환경</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>과학 + 교양</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>정다혜</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>수학</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>수학Ⅰ, 실용 경제</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>교양 + 수학</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>정대교</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>체육</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>스포츠 생활, 운동과 건강, 체육1</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>정래호</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>영어</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>영어Ⅰ, 영어권 문화</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>정빛나</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>과학탐구실험1, 생명과학Ⅰ, 통합과학1</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>정영신</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>* 고객 필요정보 제공, * 고객관리 계획수립, * 사무자동화 프로그램 활용, 상업 경제</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>기타 + 전문 교과 + 정보</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>천원영</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>동아시아사</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>최효진</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>제2외국어</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>일본어Ⅰ</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>허원아</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>예술</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>음악, 음악 감상과 비평</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>황주현</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>교양</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="D52" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E43" s="2" t="n">
+      <c r="E52" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>보건</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>전체 교사수</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n"/>
-      <c r="G44" s="2" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>전체 시수</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n">
-        <v>461</v>
-      </c>
-      <c r="E45" s="2" t="n"/>
-      <c r="F45" s="2" t="n"/>
-      <c r="G45" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n">
+        <v>722</v>
+      </c>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3889,7 +5823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B92"/>
+  <dimension ref="A1:B109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3927,7 +5861,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -3937,7 +5871,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>54.8</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5">
@@ -3947,7 +5881,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -3957,7 +5891,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>26.2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -3967,7 +5901,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -3977,7 +5911,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>11.9</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="9">
@@ -3987,7 +5921,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -3997,870 +5931,1050 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>7.1</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>5과목_교사수</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>5과목_비율</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>과학_교과(군)_교사수</t>
         </is>
       </c>
-      <c r="B11" s="4">
+      <c r="B13" s="4">
         <f>COUNTIF('교사별총시수'!$C:$C,"*과학*")</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>과학_교과(군)_교사의_총시수</t>
         </is>
       </c>
-      <c r="B12" s="4">
+      <c r="B14" s="4">
         <f>SUMIFS('교사별총시수'!$D:$D,'교사별총시수'!$C:$C,"*과학*")</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>과학_교과(군)_과목의_총시수</t>
         </is>
       </c>
-      <c r="B13" s="4">
+      <c r="B15" s="4">
         <f>SUMIFS('교사별시수현황'!$D:$D,'교사별시수현황'!$E:$E,"과학")</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>과학_교과(군)_교사의_평균시수</t>
         </is>
       </c>
-      <c r="B14" s="5">
+      <c r="B16" s="5">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*과학*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>과학_교과(군)_교사의_평균과목수</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B17" s="3" t="n">
         <v>2.8</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>교양_교과(군)_교사수</t>
         </is>
       </c>
-      <c r="B16" s="4">
+      <c r="B18" s="4">
         <f>COUNTIF('교사별총시수'!$C:$C,"*교양*")</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>교양_교과(군)_교사의_총시수</t>
         </is>
       </c>
-      <c r="B17" s="4">
+      <c r="B19" s="4">
         <f>SUMIFS('교사별총시수'!$D:$D,'교사별총시수'!$C:$C,"*교양*")</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>교양_교과(군)_과목의_총시수</t>
         </is>
       </c>
-      <c r="B18" s="4">
+      <c r="B20" s="4">
         <f>SUMIFS('교사별시수현황'!$D:$D,'교사별시수현황'!$E:$E,"교양")</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>교양_교과(군)_교사의_평균시수</t>
         </is>
       </c>
-      <c r="B19" s="5">
+      <c r="B21" s="5">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*교양*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>교양_교과(군)_교사의_평균과목수</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B22" s="6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>국어_교과(군)_교사수</t>
         </is>
       </c>
-      <c r="B21" s="4">
+      <c r="B23" s="4">
         <f>COUNTIF('교사별총시수'!$C:$C,"*국어*")</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>국어_교과(군)_교사의_총시수</t>
         </is>
       </c>
-      <c r="B22" s="4">
+      <c r="B24" s="4">
         <f>SUMIFS('교사별총시수'!$D:$D,'교사별총시수'!$C:$C,"*국어*")</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>국어_교과(군)_과목의_총시수</t>
         </is>
       </c>
-      <c r="B23" s="4">
+      <c r="B25" s="4">
         <f>SUMIFS('교사별시수현황'!$D:$D,'교사별시수현황'!$E:$E,"국어")</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>국어_교과(군)_교사의_평균시수</t>
         </is>
       </c>
-      <c r="B24" s="5">
+      <c r="B26" s="5">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*국어*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>국어_교과(군)_교사의_평균과목수</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="B27" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>기타_교과(군)_교사수</t>
+        </is>
+      </c>
+      <c r="B28" s="4">
+        <f>COUNTIF('교사별총시수'!$C:$C,"*기타*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>기타_교과(군)_교사의_총시수</t>
+        </is>
+      </c>
+      <c r="B29" s="4">
+        <f>SUMIFS('교사별총시수'!$D:$D,'교사별총시수'!$C:$C,"*기타*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>기타_교과(군)_과목의_총시수</t>
+        </is>
+      </c>
+      <c r="B30" s="4">
+        <f>SUMIFS('교사별시수현황'!$D:$D,'교사별시수현황'!$E:$E,"기타")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>기타_교과(군)_교사의_평균시수</t>
+        </is>
+      </c>
+      <c r="B31" s="5">
+        <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*기타*",'교사별총시수'!$D:$D),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>기타_교과(군)_교사의_평균과목수</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>사회_교과(군)_교사수</t>
         </is>
       </c>
-      <c r="B26" s="4">
+      <c r="B33" s="4">
         <f>COUNTIF('교사별총시수'!$C:$C,"*사회*")</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>사회_교과(군)_교사의_총시수</t>
         </is>
       </c>
-      <c r="B27" s="4">
+      <c r="B34" s="4">
         <f>SUMIFS('교사별총시수'!$D:$D,'교사별총시수'!$C:$C,"*사회*")</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>사회_교과(군)_과목의_총시수</t>
         </is>
       </c>
-      <c r="B28" s="4">
+      <c r="B35" s="4">
         <f>SUMIFS('교사별시수현황'!$D:$D,'교사별시수현황'!$E:$E,"사회")</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>사회_교과(군)_교사의_평균시수</t>
         </is>
       </c>
-      <c r="B29" s="5">
+      <c r="B36" s="5">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*사회*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>사회_교과(군)_교사의_평균과목수</t>
         </is>
       </c>
-      <c r="B30" s="8" t="n">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="B37" s="9" t="n">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>수학_교과(군)_교사수</t>
         </is>
       </c>
-      <c r="B31" s="4">
+      <c r="B38" s="4">
         <f>COUNTIF('교사별총시수'!$C:$C,"*수학*")</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>수학_교과(군)_교사의_총시수</t>
         </is>
       </c>
-      <c r="B32" s="4">
+      <c r="B39" s="4">
         <f>SUMIFS('교사별총시수'!$D:$D,'교사별총시수'!$C:$C,"*수학*")</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>수학_교과(군)_과목의_총시수</t>
         </is>
       </c>
-      <c r="B33" s="4">
+      <c r="B40" s="4">
         <f>SUMIFS('교사별시수현황'!$D:$D,'교사별시수현황'!$E:$E,"수학")</f>
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>수학_교과(군)_교사의_평균시수</t>
         </is>
       </c>
-      <c r="B34" s="5">
+      <c r="B41" s="5">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*수학*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>수학_교과(군)_교사의_평균과목수</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="B42" s="10" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>영어_교과(군)_교사수</t>
         </is>
       </c>
-      <c r="B36" s="4">
+      <c r="B43" s="4">
         <f>COUNTIF('교사별총시수'!$C:$C,"*영어*")</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>영어_교과(군)_교사의_총시수</t>
         </is>
       </c>
-      <c r="B37" s="4">
+      <c r="B44" s="4">
         <f>SUMIFS('교사별총시수'!$D:$D,'교사별총시수'!$C:$C,"*영어*")</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>영어_교과(군)_과목의_총시수</t>
         </is>
       </c>
-      <c r="B38" s="4">
+      <c r="B45" s="4">
         <f>SUMIFS('교사별시수현황'!$D:$D,'교사별시수현황'!$E:$E,"영어")</f>
         <v/>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>영어_교과(군)_교사의_평균시수</t>
         </is>
       </c>
-      <c r="B39" s="5">
+      <c r="B46" s="5">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*영어*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>영어_교과(군)_교사의_평균과목수</t>
         </is>
       </c>
-      <c r="B40" s="10" t="n">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="B47" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>예술_교과(군)_교사수</t>
         </is>
       </c>
-      <c r="B41" s="4">
+      <c r="B48" s="4">
         <f>COUNTIF('교사별총시수'!$C:$C,"*예술*")</f>
         <v/>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>예술_교과(군)_교사의_총시수</t>
         </is>
       </c>
-      <c r="B42" s="4">
+      <c r="B49" s="4">
         <f>SUMIFS('교사별총시수'!$D:$D,'교사별총시수'!$C:$C,"*예술*")</f>
         <v/>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>예술_교과(군)_과목의_총시수</t>
         </is>
       </c>
-      <c r="B43" s="4">
+      <c r="B50" s="4">
         <f>SUMIFS('교사별시수현황'!$D:$D,'교사별시수현황'!$E:$E,"예술")</f>
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>예술_교과(군)_교사의_평균시수</t>
         </is>
       </c>
-      <c r="B44" s="5">
+      <c r="B51" s="5">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*예술*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t>예술_교과(군)_교사의_평균과목수</t>
         </is>
       </c>
-      <c r="B45" s="11" t="n">
+      <c r="B52" s="12" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>전문 교과_교과(군)_교사수</t>
         </is>
       </c>
-      <c r="B46" s="4">
+      <c r="B53" s="4">
         <f>COUNTIF('교사별총시수'!$C:$C,"*전문 교과*")</f>
         <v/>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="12" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
         <is>
           <t>전문 교과_교과(군)_교사의_총시수</t>
         </is>
       </c>
-      <c r="B47" s="4">
+      <c r="B54" s="4">
         <f>SUMIFS('교사별총시수'!$D:$D,'교사별총시수'!$C:$C,"*전문 교과*")</f>
         <v/>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr">
         <is>
           <t>전문 교과_교과(군)_과목의_총시수</t>
         </is>
       </c>
-      <c r="B48" s="4">
+      <c r="B55" s="4">
         <f>SUMIFS('교사별시수현황'!$D:$D,'교사별시수현황'!$E:$E,"전문 교과")</f>
         <v/>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="12" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
         <is>
           <t>전문 교과_교과(군)_교사의_평균시수</t>
         </is>
       </c>
-      <c r="B49" s="5">
+      <c r="B56" s="5">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*전문 교과*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="12" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="13" t="inlineStr">
         <is>
           <t>전문 교과_교과(군)_교사의_평균과목수</t>
         </is>
       </c>
-      <c r="B50" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="B57" s="13" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>정보_교과(군)_교사수</t>
+        </is>
+      </c>
+      <c r="B58" s="4">
+        <f>COUNTIF('교사별총시수'!$C:$C,"*정보*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>정보_교과(군)_교사의_총시수</t>
+        </is>
+      </c>
+      <c r="B59" s="4">
+        <f>SUMIFS('교사별총시수'!$D:$D,'교사별총시수'!$C:$C,"*정보*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>정보_교과(군)_과목의_총시수</t>
+        </is>
+      </c>
+      <c r="B60" s="4">
+        <f>SUMIFS('교사별시수현황'!$D:$D,'교사별시수현황'!$E:$E,"정보")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>정보_교과(군)_교사의_평균시수</t>
+        </is>
+      </c>
+      <c r="B61" s="5">
+        <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*정보*",'교사별총시수'!$D:$D),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>정보_교과(군)_교사의_평균과목수</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="15" t="inlineStr">
         <is>
           <t>제2외국어_교과(군)_교사수</t>
         </is>
       </c>
-      <c r="B51" s="4">
+      <c r="B63" s="4">
         <f>COUNTIF('교사별총시수'!$C:$C,"*제2외국어*")</f>
         <v/>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="15" t="inlineStr">
         <is>
           <t>제2외국어_교과(군)_교사의_총시수</t>
         </is>
       </c>
-      <c r="B52" s="4">
+      <c r="B64" s="4">
         <f>SUMIFS('교사별총시수'!$D:$D,'교사별총시수'!$C:$C,"*제2외국어*")</f>
         <v/>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="15" t="inlineStr">
         <is>
           <t>제2외국어_교과(군)_과목의_총시수</t>
         </is>
       </c>
-      <c r="B53" s="4">
+      <c r="B65" s="4">
         <f>SUMIFS('교사별시수현황'!$D:$D,'교사별시수현황'!$E:$E,"제2외국어")</f>
         <v/>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="15" t="inlineStr">
         <is>
           <t>제2외국어_교과(군)_교사의_평균시수</t>
         </is>
       </c>
-      <c r="B54" s="5">
+      <c r="B66" s="5">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*제2외국어*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="15" t="inlineStr">
         <is>
           <t>제2외국어_교과(군)_교사의_평균과목수</t>
         </is>
       </c>
-      <c r="B55" s="3" t="n">
+      <c r="B67" s="15" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="16" t="inlineStr">
         <is>
           <t>체육_교과(군)_교사수</t>
         </is>
       </c>
-      <c r="B56" s="4">
+      <c r="B68" s="4">
         <f>COUNTIF('교사별총시수'!$C:$C,"*체육*")</f>
         <v/>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="16" t="inlineStr">
         <is>
           <t>체육_교과(군)_교사의_총시수</t>
         </is>
       </c>
-      <c r="B57" s="4">
+      <c r="B69" s="4">
         <f>SUMIFS('교사별총시수'!$D:$D,'교사별총시수'!$C:$C,"*체육*")</f>
         <v/>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="16" t="inlineStr">
         <is>
           <t>체육_교과(군)_과목의_총시수</t>
         </is>
       </c>
-      <c r="B58" s="4">
+      <c r="B70" s="4">
         <f>SUMIFS('교사별시수현황'!$D:$D,'교사별시수현황'!$E:$E,"체육")</f>
         <v/>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="16" t="inlineStr">
         <is>
           <t>체육_교과(군)_교사의_평균시수</t>
         </is>
       </c>
-      <c r="B59" s="5">
+      <c r="B71" s="5">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*체육*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="16" t="inlineStr">
         <is>
           <t>체육_교과(군)_교사의_평균과목수</t>
         </is>
       </c>
-      <c r="B60" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="inlineStr">
+      <c r="B72" s="16" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="17" t="inlineStr">
         <is>
           <t>한문_교과(군)_교사수</t>
         </is>
       </c>
-      <c r="B61" s="4">
+      <c r="B73" s="4">
         <f>COUNTIF('교사별총시수'!$C:$C,"*한문*")</f>
         <v/>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="7" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="17" t="inlineStr">
         <is>
           <t>한문_교과(군)_교사의_총시수</t>
         </is>
       </c>
-      <c r="B62" s="4">
+      <c r="B74" s="4">
         <f>SUMIFS('교사별총시수'!$D:$D,'교사별총시수'!$C:$C,"*한문*")</f>
         <v/>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="7" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="17" t="inlineStr">
         <is>
           <t>한문_교과(군)_과목의_총시수</t>
         </is>
       </c>
-      <c r="B63" s="4">
+      <c r="B75" s="4">
         <f>SUMIFS('교사별시수현황'!$D:$D,'교사별시수현황'!$E:$E,"한문")</f>
         <v/>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="7" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="17" t="inlineStr">
         <is>
           <t>한문_교과(군)_교사의_평균시수</t>
         </is>
       </c>
-      <c r="B64" s="5">
+      <c r="B76" s="5">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*한문*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="17" t="inlineStr">
         <is>
           <t>한문_교과(군)_교사의_평균과목수</t>
         </is>
       </c>
-      <c r="B65" s="7" t="n">
+      <c r="B77" s="17" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>1개교과군_교사수</t>
         </is>
       </c>
-      <c r="B66" s="2" t="n">
+      <c r="B78" s="2" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>1개교과군_비율</t>
         </is>
       </c>
-      <c r="B67" s="2" t="n">
-        <v>90.5</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="B79" s="2" t="n">
+        <v>74.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>2개교과군_교사수</t>
         </is>
       </c>
-      <c r="B68" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="B80" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>2개교과군_비율</t>
         </is>
       </c>
-      <c r="B69" s="2" t="n">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="B81" s="2" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>3개교과군_교사수</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>3개교과군_비율</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>전체_교사수 👩‍🏫</t>
         </is>
       </c>
-      <c r="B70" s="2" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="B84" s="2" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>전체_시수 ⏱️</t>
         </is>
       </c>
-      <c r="B71" s="2" t="n">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="B85" s="2" t="n">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>평균시수 📊</t>
         </is>
       </c>
-      <c r="B72" s="13" t="n">
-        <v>10.98</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="B86" s="18" t="n">
+        <v>14.16</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>전체_과목수 📚</t>
         </is>
       </c>
-      <c r="B73" s="2" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="B87" s="2" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>개설_과목수 🆕</t>
         </is>
       </c>
-      <c r="B74" s="2" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="B88" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>평균_과목수 💡</t>
         </is>
       </c>
-      <c r="B75" s="2" t="n">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="n"/>
-      <c r="B76" s="2" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="B89" s="2" t="n">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n"/>
+      <c r="B90" s="2" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>과학</t>
         </is>
       </c>
-      <c r="B77" s="4">
+      <c r="B91" s="4">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*과학*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>교양</t>
         </is>
       </c>
-      <c r="B78" s="4">
+      <c r="B92" s="4">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*교양*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="7" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
         <is>
           <t>국어</t>
         </is>
       </c>
-      <c r="B79" s="4">
+      <c r="B93" s="4">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*국어*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="8" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B94" s="4">
+        <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*기타*",'교사별총시수'!$D:$D),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
         <is>
           <t>사회</t>
         </is>
       </c>
-      <c r="B80" s="4">
+      <c r="B95" s="4">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*사회*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="9" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
         <is>
           <t>수학</t>
         </is>
       </c>
-      <c r="B81" s="4">
+      <c r="B96" s="4">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*수학*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="10" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="11" t="inlineStr">
         <is>
           <t>영어</t>
         </is>
       </c>
-      <c r="B82" s="4">
+      <c r="B97" s="4">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*영어*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="11" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="12" t="inlineStr">
         <is>
           <t>예술</t>
         </is>
       </c>
-      <c r="B83" s="4">
+      <c r="B98" s="4">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*예술*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="12" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="13" t="inlineStr">
         <is>
           <t>전문 교과</t>
         </is>
       </c>
-      <c r="B84" s="4">
+      <c r="B99" s="4">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*전문 교과*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="14" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="B100" s="4">
+        <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*정보*",'교사별총시수'!$D:$D),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="inlineStr">
         <is>
           <t>제2외국어</t>
         </is>
       </c>
-      <c r="B85" s="4">
+      <c r="B101" s="4">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*제2외국어*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="6" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="16" t="inlineStr">
         <is>
           <t>체육</t>
         </is>
       </c>
-      <c r="B86" s="4">
+      <c r="B102" s="4">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*체육*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="7" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="17" t="inlineStr">
         <is>
           <t>한문</t>
         </is>
       </c>
-      <c r="B87" s="4">
+      <c r="B103" s="4">
         <f>IFERROR(AVERAGEIF('교사별총시수'!$C:$C,"*한문*",'교사별총시수'!$D:$D),0)</f>
         <v/>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="n"/>
-      <c r="B88" s="2" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="n"/>
+      <c r="B104" s="2" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>1과목</t>
         </is>
       </c>
-      <c r="B89" s="2" t="n">
-        <v>54.8</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="B105" s="2" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>2과목</t>
         </is>
       </c>
-      <c r="B90" s="2" t="n">
-        <v>26.2</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="B106" s="2" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>3과목</t>
         </is>
       </c>
-      <c r="B91" s="2" t="n">
-        <v>11.9</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="B107" s="2" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>4과목</t>
         </is>
       </c>
-      <c r="B92" s="2" t="n">
-        <v>7.1</v>
+      <c r="B108" s="2" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>5과목</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -4875,13 +6989,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4900,7 +7014,7 @@
           <t>교사수</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="19" t="inlineStr">
         <is>
           <t>해당 교사명</t>
         </is>
@@ -4914,15 +7028,15 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>과학 + 교양</t>
+          <t>기타 + 전문 교과 + 정보</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>전형구</t>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>정영신</t>
         </is>
       </c>
     </row>
@@ -4934,15 +7048,15 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>교양 + 수학</t>
+          <t>과학 + 교양</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
-        <is>
-          <t>이애림, 정다혜</t>
+        <v>1</v>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>전형구</t>
         </is>
       </c>
     </row>
@@ -4954,15 +7068,75 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>교양 + 수학</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>이애림, 정다혜</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>교양 + 체육</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>임영수</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>기타 + 전문 교과</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>김소형, 김혜주, 문기현, 배서연, 엄미희, 전정화</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>단일학교</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>전문 교과 + 정보</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>인창열, 임건</t>
         </is>
       </c>
     </row>
